--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-11-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£9.72</t>
+          <t>£9.70</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -703,7 +703,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£11.13</t>
+          <t>£11.09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -943,7 +943,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£14.66</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£18.19</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£20.50</t>
+          <t>£20.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£20.35</t>
+          <t>£20.30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£23.58</t>
+          <t>£23.38</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£25.59</t>
+          <t>£25.40</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£25.10</t>
+          <t>£25.00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£30.48</t>
+          <t>£30.40</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£37.66</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£26.90</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£33.23</t>
+          <t>£31.65</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£32.90</t>
+          <t>£31.05</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£34.20</t>
+          <t>£34.15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£35.90</t>
+          <t>£34.10</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£40.90</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff726f2a235
-	0x7ff726c82630
-	0x7ff726a116dd
-	0x7ff726a6a27e
-	0x7ff726a6a58c
-	0x7ff726abed77
-	0x7ff726abbaba
-	0x7ff726a5b0ed
-	0x7ff726a5bf63
-	0x7ff726f55d60
-	0x7ff726f4fe8a
-	0x7ff726f71005
-	0x7ff726c9d71e
-	0x7ff726ca4e1f
-	0x7ff726c8b7c4
-	0x7ff726c8b97f
-	0x7ff726c718e8
+	0x7ff727d5a235
+	0x7ff727ab2630
+	0x7ff7278416dd
+	0x7ff72789a27e
+	0x7ff72789a58c
+	0x7ff7278eed77
+	0x7ff7278ebaba
+	0x7ff72788b0ed
+	0x7ff72788bf63
+	0x7ff727d85d60
+	0x7ff727d7fe8a
+	0x7ff727da1005
+	0x7ff727acd71e
+	0x7ff727ad4e1f
+	0x7ff727abb7c4
+	0x7ff727abb97f
+	0x7ff727aa18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
